--- a/experiment/DAT_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/DAT_bestx4/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.03</v>
+        <v>24.05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5722</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         <v>28.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8129</v>
+        <v>0.8132</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.54</v>
+        <v>26.57</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8124</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.66</v>
+        <v>30.67</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8495</v>
+        <v>0.8497</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.27</v>
+        <v>26.29</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7114</v>
+        <v>0.7122000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>33.9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8932</v>
+        <v>0.8933</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.31</v>
+        <v>26.33</v>
       </c>
       <c r="C8" t="n">
-        <v>0.751</v>
+        <v>0.7521</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.14</v>
+        <v>23.15</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5947</v>
+        <v>0.5956</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         <v>27.49</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.7889</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.32</v>
+        <v>29.33</v>
       </c>
       <c r="C11" t="n">
-        <v>0.803</v>
+        <v>0.8034</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.59</v>
+        <v>24.62</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7342</v>
+        <v>0.7371</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.11</v>
+        <v>28.13</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7571</v>
+        <v>0.7582</v>
       </c>
     </row>
     <row r="14">
@@ -611,7 +611,7 @@
         <v>30.07</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8094</v>
+        <v>0.8097</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.35</v>
+        <v>29.41</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8324</v>
+        <v>0.8336</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.11</v>
+        <v>25.12</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6814</v>
+        <v>0.6824</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.88</v>
+        <v>24.91</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7609</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.78</v>
+        <v>34.79</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8938</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         <v>32.93</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8933</v>
+        <v>0.8935</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.28</v>
+        <v>26.31</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7388</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.12</v>
+        <v>26.13</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8017</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.32</v>
+        <v>22.34</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6944</v>
+        <v>0.6961000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.91</v>
+        <v>23.92</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         <v>24.85</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5744</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.62</v>
+        <v>26.64</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7936</v>
+        <v>0.7946</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>27.74</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8232</v>
+        <v>0.8233</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.08</v>
+        <v>27.1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8396</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.82</v>
+        <v>27.81</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7396</v>
+        <v>0.7393</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.64</v>
+        <v>29.65</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8031</v>
+        <v>0.8037</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.55</v>
+        <v>32.59</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9026</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         <v>19.92</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5073</v>
+        <v>0.5078</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.8</v>
+        <v>29.81</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8183</v>
+        <v>0.8185</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.95</v>
+        <v>20.96</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4294</v>
+        <v>0.4303</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.21</v>
+        <v>25.23</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6725</v>
+        <v>0.6734</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.49</v>
+        <v>24.5</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7589</v>
+        <v>0.7598</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.9</v>
+        <v>34.92</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27.05</v>
+        <v>27.08</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7441</v>
       </c>
     </row>
     <row r="38">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.27</v>
+        <v>28.28</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7188</v>
+        <v>0.7194</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         <v>28.52</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7469</v>
+        <v>0.7466</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35.79</v>
+        <v>35.82</v>
       </c>
       <c r="C41" t="n">
-        <v>0.953</v>
+        <v>0.9535</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.91</v>
+        <v>26.93</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7467</v>
+        <v>0.7474</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.89</v>
+        <v>25.9</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7239</v>
+        <v>0.7243000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.84</v>
+        <v>26.86</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7617</v>
+        <v>0.7624</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.03</v>
+        <v>28.05</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8766</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.81</v>
+        <v>24.83</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6827</v>
+        <v>0.6836</v>
       </c>
     </row>
     <row r="47">
@@ -1040,7 +1040,7 @@
         <v>34.72</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8716</v>
+        <v>0.8717</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.84</v>
+        <v>22.85</v>
       </c>
       <c r="C48" t="n">
-        <v>0.627</v>
+        <v>0.6279</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>25.02</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6371</v>
+        <v>0.6373</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.41</v>
+        <v>27.47</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8778</v>
+        <v>0.8794</v>
       </c>
     </row>
     <row r="51">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.87</v>
+        <v>24.88</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6212</v>
+        <v>0.6216</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.75</v>
+        <v>22.76</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7095</v>
+        <v>0.7097</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.38</v>
+        <v>32.44</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8438</v>
+        <v>0.8448</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.57</v>
+        <v>32.58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8003</v>
+        <v>0.8006</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.8</v>
+        <v>27.84</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7786</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.67</v>
+        <v>25.7</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6972</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>21.49</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4265</v>
+        <v>0.4274</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.5</v>
+        <v>27.52</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7282</v>
+        <v>0.7288</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1209,7 @@
         <v>32.04</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7932</v>
+        <v>0.7933</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.22</v>
+        <v>31.24</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7849</v>
+        <v>0.7852</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.74</v>
+        <v>31.75</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8153</v>
+        <v>0.8155</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28.96</v>
+        <v>28.94</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.7937</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33.49</v>
+        <v>33.59</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9517</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.35</v>
+        <v>24.37</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6734</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         <v>26.06</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6234</v>
+        <v>0.6236</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.39</v>
+        <v>28.41</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7957</v>
+        <v>0.7963</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>39.9</v>
+        <v>39.98</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9807</v>
+        <v>0.9808</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.1</v>
+        <v>21.11</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5832000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.81</v>
+        <v>22.82</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6513</v>
+        <v>0.6521</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>28.93</v>
+        <v>28.99</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8099</v>
+        <v>0.8111</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.49</v>
+        <v>30.53</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8176</v>
+        <v>0.8187</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         <v>25.49</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5985</v>
       </c>
     </row>
     <row r="74">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.32</v>
+        <v>26.33</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6979</v>
+        <v>0.6983</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.2</v>
+        <v>24.22</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6997</v>
+        <v>0.7008</v>
       </c>
     </row>
     <row r="77">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.7</v>
+        <v>30.71</v>
       </c>
       <c r="C77" t="n">
         <v>0.7859</v>
@@ -1443,7 +1443,7 @@
         <v>23.69</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4799</v>
+        <v>0.4802</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         <v>29.83</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8111</v>
+        <v>0.8113</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.72</v>
+        <v>32.78</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9515</v>
+        <v>0.9518</v>
       </c>
     </row>
     <row r="81">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.79</v>
+        <v>29.8</v>
       </c>
       <c r="C81" t="n">
         <v>0.82</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.79</v>
+        <v>35.83</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9393</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.52</v>
+        <v>28.53</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7181</v>
+        <v>0.7188</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.28</v>
+        <v>22.29</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5311</v>
+        <v>0.5318000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21.11</v>
+        <v>21.12</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6082</v>
+        <v>0.6093</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.73</v>
+        <v>25.74</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7907</v>
+        <v>0.7919</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25.03</v>
+        <v>25.04</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6047</v>
+        <v>0.6055</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.38</v>
+        <v>27.39</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6954</v>
+        <v>0.6965</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.69</v>
+        <v>30.71</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8132</v>
+        <v>0.8137</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         <v>27.25</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5621</v>
+        <v>0.5623</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.13</v>
+        <v>25.16</v>
       </c>
       <c r="C91" t="n">
-        <v>0.648</v>
+        <v>0.6495</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>29.18</v>
+        <v>29.19</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7159</v>
+        <v>0.7161</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.69</v>
+        <v>26.77</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7539</v>
+        <v>0.7573</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.82</v>
+        <v>30.9</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8787</v>
+        <v>0.8789</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26.02</v>
+        <v>26.04</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7183</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.39</v>
+        <v>26.46</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8087</v>
+        <v>0.8107</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21.94</v>
+        <v>21.95</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3198</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1703,7 @@
         <v>27.04</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5633</v>
+        <v>0.5634</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.39</v>
+        <v>26.4</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7809</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.93</v>
+        <v>26.94</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7357</v>
+        <v>0.7363</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.15</v>
+        <v>25.18</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7289</v>
+        <v>0.7308</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.59</v>
+        <v>27.6</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7373</v>
+        <v>0.738</v>
       </c>
     </row>
   </sheetData>
